--- a/vse-loti/340044065/spec-340044065.xlsx
+++ b/vse-loti/340044065/spec-340044065.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.00&quot; ₽&quot;"/>
+  </numFmts>
   <fonts count="4">
     <font>
       <name val="Calibri"/>
@@ -33,11 +35,11 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <b val="1"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -80,13 +82,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -454,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -516,34 +522,62 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>ИТОГО</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Труба стальная электросварная круглая Идентификатор: 222012436 (КТРУ 24.20.13.130-00000004)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Погонный метр</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" s="4" t="n">
+        <v>50649.48</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Документация проверена, НМЦК в явном виде не указан</t>
-        </is>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>50649.48</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Источник: Проект_контракта.docx
-НМЦК.docx
-Описание объекта закупки.docx
-Требование к содержанию заявки (преимущество).docx</t>
-        </is>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>НМЦК из обоснования:</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>2905123</v>
       </c>
     </row>
-    <row r="6"/>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Источник: Проект_контракта.docx</t>
+        </is>
+      </c>
+    </row>
     <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A5:B7"/>
+    <mergeCell ref="A6:B8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vse-loti/340044065/spec-340044065.xlsx
+++ b/vse-loti/340044065/spec-340044065.xlsx
@@ -16,8 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00&quot; ₽&quot;"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00&quot; ₽&quot;"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -82,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -90,8 +91,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -460,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -527,57 +530,280 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная круглая Идентификатор: 222012436 (КТРУ 24.20.13.130-00000004)</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>Труба стальная электросварная круглая Идентификатор: 222012436 (КТРУ 24.20.13.130-00000004) 57×4 (КТРУ 24.20.13.130-00000004)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>57×4</t>
+        </is>
+      </c>
       <c r="D2" s="3" t="n">
-        <v>126</v>
+        <v>18</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Погонный метр</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" s="4" t="n">
+      <c r="F2" s="4" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>7235.64</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>76974.89</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>92369.87</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Труба стальная электросварная круглая Идентификатор: 222012436 (КТРУ 24.20.13.130-00000004) 76×4 (КТРУ 24.20.13.130-00000004)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>76×4</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Погонный метр</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>7235.64</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>56528.44</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>67834.12</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Труба стальная электросварная круглая Идентификатор: 222012436 (КТРУ 24.20.13.130-00000004) 89×4 (КТРУ 24.20.13.130-00000004)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>89×4</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Погонный метр</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>7235.64</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>47918.15</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>57501.77</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Труба стальная электросварная круглая Идентификатор: 222012436 (КТРУ 24.20.13.130-00000004) 108×5 (КТРУ 24.20.13.130-00000004)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>108×5</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Погонный метр</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>0.229</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>7235.64</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>31596.68</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>37916.02</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Труба стальная электросварная круглая Идентификатор: 222012436 (КТРУ 24.20.13.130-00000004) 114×5 (КТРУ 24.20.13.130-00000004)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>114×5</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Погонный метр</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>0.242</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>7235.64</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>29899.34</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>35879.21</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Труба стальная электросварная круглая Идентификатор: 222012436 (КТРУ 24.20.13.130-00000004) 159×5 (КТРУ 24.20.13.130-00000004)</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>159×5</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Погонный метр</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>7235.64</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>21156.84</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>25388.21</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Труба стальная электросварная круглая Идентификатор: 222012436 (КТРУ 24.20.13.130-00000004) 219×6 (КТРУ 24.20.13.130-00000004)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>219×6</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Погонный метр</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>7235.64</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>12761.27</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>15313.52</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>1.753</v>
+      </c>
+      <c r="G9" s="8" t="n">
         <v>50649.48</v>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>ИТОГО</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="n">
-        <v>50649.48</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="G10" s="8" t="n">
         <v>2905123</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Источник: Проект_контракта.docx</t>
         </is>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
+    <row r="13"/>
+    <row r="14"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:B8"/>
+    <mergeCell ref="A12:B14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vse-loti/340044065/spec-340044065.xlsx
+++ b/vse-loti/340044065/spec-340044065.xlsx
@@ -16,9 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00&quot; ₽&quot;"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.00&quot; ₽&quot;"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -83,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -91,10 +90,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -463,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -530,34 +527,24 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная круглая Идентификатор: 222012436 (КТРУ 24.20.13.130-00000004) 57×4 (КТРУ 24.20.13.130-00000004)</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>57×4</t>
-        </is>
-      </c>
+          <t>Труба стальная электросварная круглая Идентификатор: 222012436 (КТРУ 24.20.13.130-00000004) — все типоразмеры: 57×4; 76×4; 89×4; 108×5; 114×5; 159×5; 219×6</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" s="3" t="n">
-        <v>18</v>
+        <v>126</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Погонный метр</t>
         </is>
       </c>
-      <c r="F2" s="4" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>7235.64</v>
-      </c>
-      <c r="H2" s="5" t="n">
-        <v>76974.89</v>
-      </c>
-      <c r="I2" s="5" t="n">
-        <v>92369.87</v>
-      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" s="4" t="n">
+        <v>50649.48</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -565,34 +552,25 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная круглая Идентификатор: 222012436 (КТРУ 24.20.13.130-00000004) 76×4 (КТРУ 24.20.13.130-00000004)</t>
+          <t>Труба стальная электросварная круглая Идентификатор: 222012436 (КТРУ 24.20.13.130-00000004) — типоразмер 57×4</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>76×4</t>
+          <t>57×4</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Погонный метр</t>
         </is>
       </c>
-      <c r="F3" s="4" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>7235.64</v>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v>56528.44</v>
-      </c>
-      <c r="I3" s="5" t="n">
-        <v>67834.12</v>
-      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -600,34 +578,25 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная круглая Идентификатор: 222012436 (КТРУ 24.20.13.130-00000004) 89×4 (КТРУ 24.20.13.130-00000004)</t>
+          <t>Труба стальная электросварная круглая Идентификатор: 222012436 (КТРУ 24.20.13.130-00000004) — типоразмер 76×4</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>89×4</t>
+          <t>76×4</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Погонный метр</t>
         </is>
       </c>
-      <c r="F4" s="4" t="n">
-        <v>0.151</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>7235.64</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>47918.15</v>
-      </c>
-      <c r="I4" s="5" t="n">
-        <v>57501.77</v>
-      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -635,34 +604,25 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная круглая Идентификатор: 222012436 (КТРУ 24.20.13.130-00000004) 108×5 (КТРУ 24.20.13.130-00000004)</t>
+          <t>Труба стальная электросварная круглая Идентификатор: 222012436 (КТРУ 24.20.13.130-00000004) — типоразмер 89×4</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>108×5</t>
+          <t>89×4</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Погонный метр</t>
         </is>
       </c>
-      <c r="F5" s="4" t="n">
-        <v>0.229</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>7235.64</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>31596.68</v>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v>37916.02</v>
-      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -670,34 +630,25 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная круглая Идентификатор: 222012436 (КТРУ 24.20.13.130-00000004) 114×5 (КТРУ 24.20.13.130-00000004)</t>
+          <t>Труба стальная электросварная круглая Идентификатор: 222012436 (КТРУ 24.20.13.130-00000004) — типоразмер 108×5</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>114×5</t>
+          <t>108×5</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Погонный метр</t>
         </is>
       </c>
-      <c r="F6" s="4" t="n">
-        <v>0.242</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>7235.64</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>29899.34</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>35879.21</v>
-      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -705,34 +656,25 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная круглая Идентификатор: 222012436 (КТРУ 24.20.13.130-00000004) 159×5 (КТРУ 24.20.13.130-00000004)</t>
+          <t>Труба стальная электросварная круглая Идентификатор: 222012436 (КТРУ 24.20.13.130-00000004) — типоразмер 114×5</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>159×5</t>
+          <t>114×5</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Погонный метр</t>
         </is>
       </c>
-      <c r="F7" s="4" t="n">
-        <v>0.342</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>7235.64</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>21156.84</v>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>25388.21</v>
-      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -740,70 +682,84 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная круглая Идентификатор: 222012436 (КТРУ 24.20.13.130-00000004) 219×6 (КТРУ 24.20.13.130-00000004)</t>
+          <t>Труба стальная электросварная круглая Идентификатор: 222012436 (КТРУ 24.20.13.130-00000004) — типоразмер 159×5</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>159×5</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Погонный метр</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Труба стальная электросварная круглая Идентификатор: 222012436 (КТРУ 24.20.13.130-00000004) — типоразмер 219×6</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
           <t>219×6</t>
         </is>
       </c>
-      <c r="D8" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Погонный метр</t>
         </is>
       </c>
-      <c r="F8" s="4" t="n">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>7235.64</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>12761.27</v>
-      </c>
-      <c r="I8" s="5" t="n">
-        <v>15313.52</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="F9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="F9" s="7" t="n">
-        <v>1.753</v>
-      </c>
-      <c r="G9" s="8" t="n">
+      <c r="G10" s="6" t="n">
         <v>50649.48</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="G10" s="8" t="n">
+      <c r="G11" s="6" t="n">
         <v>2905123</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Источник: Проект_контракта.docx</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14"/>
+    <row r="15"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A12:B14"/>
+    <mergeCell ref="A13:B15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vse-loti/340044065/spec-340044065.xlsx
+++ b/vse-loti/340044065/spec-340044065.xlsx
@@ -16,8 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00&quot; ₽&quot;"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00&quot; ₽&quot;"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -82,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -90,8 +91,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -460,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -527,10 +530,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная круглая Идентификатор: 222012436 (КТРУ 24.20.13.130-00000004) — все типоразмеры: 57×4; 76×4; 89×4; 108×5; 114×5; 159×5; 219×6</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>Труба стальная электросварная круглая — 57×4 (КТРУ 24.20.13.130-00000004)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>57×4</t>
+        </is>
+      </c>
       <c r="D2" s="3" t="n">
         <v>126</v>
       </c>
@@ -539,227 +546,265 @@
           <t>Погонный метр</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" s="4" t="n">
+      <c r="F2" s="4" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="G2" s="5" t="n">
         <v>50649.48</v>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="H2" s="5" t="n">
+        <v>76858.09</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>92229.71000000001</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная круглая Идентификатор: 222012436 (КТРУ 24.20.13.130-00000004) — типоразмер 57×4</t>
+          <t>Труба стальная электросварная круглая — 76×4 (КТРУ 24.20.13.130-00000004)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>57×4</t>
+          <t>76×4</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Погонный метр</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="F3" s="4" t="n">
+        <v>2.556</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>196405.2</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>76840.85000000001</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>92209.00999999999</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная круглая Идентификатор: 222012436 (КТРУ 24.20.13.130-00000004) — типоразмер 76×4</t>
+          <t>Труба стальная электросварная круглая — 89×4 (КТРУ 24.20.13.130-00000004)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>76×4</t>
+          <t>89×4</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Погонный метр</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="F4" s="4" t="n">
+        <v>1.156</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>88851.3</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>76860.99000000001</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>92233.17999999999</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная круглая Идентификатор: 222012436 (КТРУ 24.20.13.130-00000004) — типоразмер 89×4</t>
+          <t>Труба стальная электросварная круглая — 108×5 (КТРУ 24.20.13.130-00000004)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>89×4</t>
+          <t>108×5</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0</v>
+        <v>732</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Погонный метр</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="F5" s="4" t="n">
+        <v>9.295999999999999</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>720229.4399999999</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>77477.35000000001</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>92972.82000000001</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная круглая Идентификатор: 222012436 (КТРУ 24.20.13.130-00000004) — типоразмер 108×5</t>
+          <t>Труба стальная электросварная круглая — 114×5 (КТРУ 24.20.13.130-00000004)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>108×5</t>
+          <t>114×5</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Погонный метр</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="F6" s="4" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>6198.78</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>76528.14999999999</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>91833.78</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная круглая Идентификатор: 222012436 (КТРУ 24.20.13.130-00000004) — типоразмер 114×5</t>
+          <t>Труба стальная электросварная круглая — 159×5 (КТРУ 24.20.13.130-00000004)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>114×5</t>
+          <t>159×5</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0</v>
+        <v>294</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Погонный метр</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="F7" s="4" t="n">
+        <v>5.583</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>425221.02</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>76163.53999999999</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>91396.24000000001</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная круглая Идентификатор: 222012436 (КТРУ 24.20.13.130-00000004) — типоразмер 159×5</t>
+          <t>Труба стальная электросварная круглая — 219×6 (КТРУ 24.20.13.130-00000004)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>159×5</t>
+          <t>219×6</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0</v>
+        <v>588</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Погонный метр</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="F8" s="4" t="n">
+        <v>18.534</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>1417568.04</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>76484.73</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>91781.67999999999</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Труба стальная электросварная круглая Идентификатор: 222012436 (КТРУ 24.20.13.130-00000004) — типоразмер 219×6</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>219×6</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Погонный метр</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>37.865</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>2905123.26</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>ИТОГО</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>50649.48</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="G10" s="8" t="n">
         <v>2905123</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Источник: Проект_контракта.docx</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Источник: Печатная форма извещения ЕИС (zakupki.gov.ru), № 0551300017426000003
+Проект_контракта.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14"/>
-    <row r="15"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A13:B15"/>
+    <mergeCell ref="A12:B14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
